--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127883190</v>
+        <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92699</v>
+        <v>92381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624283</v>
+        <v>624270</v>
       </c>
       <c r="R3" t="n">
-        <v>6853189</v>
+        <v>6853177</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,72 +875,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127883190</t>
+          <t>https://artportalen.se/Sighting/136896832</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127804095</v>
+        <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>80305</v>
+        <v>92381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624385</v>
+        <v>624236</v>
       </c>
       <c r="R4" t="n">
-        <v>6853379</v>
+        <v>6853187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,34 +977,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127804095</t>
+          <t>https://artportalen.se/Sighting/136897531</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486978</v>
+        <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>92134</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,37 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624276</v>
+        <v>624285</v>
       </c>
       <c r="R5" t="n">
-        <v>6853183</v>
+        <v>6853325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,34 +1079,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128486978</t>
+          <t>https://artportalen.se/Sighting/136894891</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127880991</v>
+        <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>92699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624038</v>
+        <v>624283</v>
       </c>
       <c r="R6" t="n">
-        <v>6853151</v>
+        <v>6853189</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,16 +1202,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127880991</t>
+          <t>https://artportalen.se/Sighting/127883190</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128048266</v>
+        <v>127804095</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>80305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1347</v>
+        <v>392</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asptagging</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Radulodon erikssonii</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ryvarden</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624247</v>
+        <v>624385</v>
       </c>
       <c r="R7" t="n">
-        <v>6853194</v>
+        <v>6853379</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,24 +1290,11 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Mattias Edman</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Maria Wallin</t>
@@ -1333,16 +1308,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128048266</t>
+          <t>https://artportalen.se/Sighting/127804095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129430851</v>
+        <v>128486978</v>
       </c>
       <c r="B8" t="n">
-        <v>93117</v>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3382</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspskinn</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Conferticium ravum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Burt) Ginns &amp; G.W. Freeman</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624267</v>
+        <v>624276</v>
       </c>
       <c r="R8" t="n">
-        <v>6853196</v>
+        <v>6853183</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,16 +1414,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129430851</t>
+          <t>https://artportalen.se/Sighting/128486978</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128715868</v>
+        <v>127880991</v>
       </c>
       <c r="B9" t="n">
-        <v>93209</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1458,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624408</v>
+        <v>624038</v>
       </c>
       <c r="R9" t="n">
-        <v>6853257</v>
+        <v>6853151</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,12 +1488,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,57 +1520,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128715868</t>
+          <t>https://artportalen.se/Sighting/127880991</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127881871</v>
+        <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>91893</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624265</v>
+        <v>624489</v>
       </c>
       <c r="R10" t="n">
-        <v>6853335</v>
+        <v>6853314</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,12 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,72 +1605,68 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127881871</t>
+          <t>https://artportalen.se/Sighting/136895598</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127882505</v>
+        <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624166</v>
+        <v>624183</v>
       </c>
       <c r="R11" t="n">
-        <v>6853271</v>
+        <v>6853169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,12 +1693,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,72 +1707,74 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127882505</t>
+          <t>https://artportalen.se/Sighting/136897922</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2083649</v>
+        <v>128048266</v>
       </c>
       <c r="B12" t="n">
-        <v>80336</v>
+        <v>92120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1347</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Asptagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Radulodon erikssonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>GULSJÖN (16H0g01), Hls</t>
+          <t>Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624278</v>
+        <v>624247</v>
       </c>
       <c r="R12" t="n">
-        <v>6853202</v>
+        <v>6853194</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,17 +1798,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1994-08-15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1994-08-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>160706011 / LEP SATU / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,78 +1812,85 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AT12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan-olov Edlund</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2083649</t>
+          <t>https://artportalen.se/Sighting/128048266</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127805341</v>
+        <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>96565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624083</v>
+        <v>624256</v>
       </c>
       <c r="R13" t="n">
-        <v>6853162</v>
+        <v>6853184</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,12 +1914,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,76 +1928,71 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127805341</t>
+          <t>https://artportalen.se/Sighting/136896511</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127805282</v>
+        <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>92327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>Gulsjön, Gulsjön, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623986</v>
+        <v>624329</v>
       </c>
       <c r="R14" t="n">
-        <v>6853147</v>
+        <v>6853310</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,12 +2016,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,62 +2030,60 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127805282</t>
+          <t>https://artportalen.se/Sighting/136895014</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127805309</v>
+        <v>129430851</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>93117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>3382</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Conferticium ravum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2126,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624037</v>
+        <v>624267</v>
       </c>
       <c r="R15" t="n">
-        <v>6853147</v>
+        <v>6853196</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2156,12 +2121,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,48 +2153,43 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127805309</t>
+          <t>https://artportalen.se/Sighting/129430851</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128619158</v>
+        <v>128715868</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2237,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623959</v>
+        <v>624408</v>
       </c>
       <c r="R16" t="n">
-        <v>6853127</v>
+        <v>6853257</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2273,11 +2233,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 70 plantor. Ett par blomstänglar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,54 +2253,49 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128619158</t>
+          <t>https://artportalen.se/Sighting/128715868</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128619219</v>
+        <v>127881871</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>91893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2353,13 +2303,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624296</v>
+        <v>624265</v>
       </c>
       <c r="R17" t="n">
-        <v>6853243</v>
+        <v>6853335</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,17 +2333,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Knappt 100 plantor.</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,22 +2359,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128619219</t>
+          <t>https://artportalen.se/Sighting/127881871</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128619291</v>
+        <v>127882505</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,31 +2382,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2469,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624359</v>
+        <v>624166</v>
       </c>
       <c r="R18" t="n">
-        <v>6853253</v>
+        <v>6853271</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,17 +2439,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor.</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,13 +2465,1743 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/127882505</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2083649</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>GULSJÖN (16H0g01), Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>624278</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6853202</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1994-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1994-08-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>160706011 / LEP SATU / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan-olov Edlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2083649</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136896952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>624257</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6853189</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136896952</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127805341</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>624083</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6853162</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127805341</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136895917</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>624445</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6853278</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136895917</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136896271</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>624397</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6853250</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Talltitefamilj</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136896271</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136894262</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>624219</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6853277</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136894262</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136894759</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>624261</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6853316</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136894759</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136897779</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>624196</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6853169</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136897779</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136894410</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>624251</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6853254</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136894410</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127805282</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623986</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6853147</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127805282</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127805309</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>624037</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6853147</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127805309</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128619158</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>623959</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6853127</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 70 plantor. Ett par blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619158</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128619219</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>624296</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6853243</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Knappt 100 plantor.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128619219</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128619291</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>624359</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6853253</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128619291</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136895241</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>624347</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6853340</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136895241</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136897755</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gulsjön, Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>624196</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6853168</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136897755</t>
         </is>
       </c>
     </row>
@@ -2559,6 +4224,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92381</v>
+        <v>92383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92381</v>
+        <v>92383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92383</v>
+        <v>92385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92383</v>
+        <v>92385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92392</v>
+        <v>92396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92392</v>
+        <v>92396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92398</v>
+        <v>92411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92398</v>
+        <v>92411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136895917</v>
       </c>
       <c r="B22" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136896271</v>
       </c>
       <c r="B23" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92411</v>
+        <v>92413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92411</v>
+        <v>92413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136895917</v>
       </c>
       <c r="B22" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>136896271</v>
       </c>
       <c r="B23" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>136894262</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>136894759</v>
       </c>
       <c r="B25" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>136897779</v>
       </c>
       <c r="B26" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2829,11 +2829,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gulsjön, Gulsjön, Hls</t>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92413</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92413</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136895917</v>
       </c>
       <c r="B22" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136896271</v>
       </c>
       <c r="B23" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136894262</v>
       </c>
       <c r="B24" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136894759</v>
       </c>
       <c r="B25" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136897779</v>
       </c>
       <c r="B26" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92427</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92427</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136895917</v>
       </c>
       <c r="B22" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136896271</v>
       </c>
       <c r="B23" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92432</v>
+        <v>92437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92432</v>
+        <v>92437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136895917</v>
       </c>
       <c r="B22" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136896271</v>
       </c>
       <c r="B23" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92437</v>
+        <v>92449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92437</v>
+        <v>92449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92449</v>
+        <v>92450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92449</v>
+        <v>92450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136896832</v>
       </c>
       <c r="B3" t="n">
-        <v>92450</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>136897531</v>
       </c>
       <c r="B4" t="n">
-        <v>92450</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>136894891</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>136895598</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136897922</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136896511</v>
       </c>
       <c r="B13" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136895014</v>
       </c>
       <c r="B14" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136896952</v>
       </c>
       <c r="B20" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>136894410</v>
       </c>
       <c r="B27" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>136895241</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>136897755</v>
       </c>
       <c r="B34" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
